--- a/sources/armorking_step5b.xlsx
+++ b/sources/armorking_step5b.xlsx
@@ -1086,6 +1086,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>28448d3f-5d22-45cc-a782-02fe9da1d852</t>
@@ -1123,6 +1128,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>da3a1275-cb0c-4106-8641-cfa9ccdf3ec7</t>
@@ -1165,6 +1175,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>c59ded73-4975-409c-9fcb-97f64f823e1f</t>
@@ -1207,6 +1222,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>4bfbb956-22f3-4aa3-8b36-b331246b3633</t>
@@ -1249,6 +1269,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>b017afe8-35fe-4676-b2eb-d81bccc55df5</t>
@@ -1301,6 +1326,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>4032df9b-cac0-4300-a750-9f6328f0125c</t>
@@ -1348,6 +1378,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>03ae734c-c034-4a04-8b1f-1969120d9045</t>
@@ -1393,6 +1428,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>f38eafdb-7ad2-4d22-a656-ee63cb402a1e</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -5438,6 +5478,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
+        </is>
+      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>df43279b-a9bb-445a-89c9-8519e6dcee4a</t>
@@ -5475,6 +5520,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>ab4325ea-0934-4517-856d-7640da4c01f7</t>
@@ -5517,6 +5567,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>d1de2b97-22f9-4d70-a0bb-b61b3d71226c</t>
@@ -5559,6 +5614,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
+        </is>
+      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>fc691ddf-15db-4695-a8e9-7430fe664066</t>
@@ -5599,6 +5659,11 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>fdcf2a53-d956-49ec-97b6-76739cea2462</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -5743,6 +5808,11 @@
           <t>hhmmhLLLmm</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>21571b37-4525-4b34-9433-0797a86f473f</t>
+        </is>
+      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>21571b37-4525-4b34-9433-0797a86f473f</t>
@@ -5773,6 +5843,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmmhLLLmm</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>3d0c8edd-a764-4366-833c-c7fe06fc9cc8</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">

--- a/sources/armorking_step5b.xlsx
+++ b/sources/armorking_step5b.xlsx
@@ -1108,6 +1108,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1153,6 +1158,11 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>– 2,1,2,2,1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2,1,2,1,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
